--- a/p6_deployment/data/england/data_preparation/clean_data/df_match_player_cleaned.xlsx
+++ b/p6_deployment/data/england/data_preparation/clean_data/df_match_player_cleaned.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A2:A45"/>
+  <dimension ref="A2:A47"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="2">
@@ -487,250 +487,264 @@
     <row r="10">
       <c r="A10" s="1" t="inlineStr">
         <is>
-          <t>tYjCfe2E</t>
+          <t>fmqtFMjD</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="1" t="inlineStr">
         <is>
-          <t>OMDVg8x9</t>
+          <t>AeRSxQrK</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="1" t="inlineStr">
         <is>
-          <t>jXcAnQUr</t>
+          <t>tYjCfe2E</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="1" t="inlineStr">
         <is>
-          <t>fRe0c20b</t>
+          <t>OMDVg8x9</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="1" t="inlineStr">
         <is>
-          <t>CnnJp4ae</t>
+          <t>jXcAnQUr</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="1" t="inlineStr">
         <is>
-          <t>bw1zAKS6</t>
+          <t>fRe0c20b</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="1" t="inlineStr">
         <is>
-          <t>GINCsvmn</t>
+          <t>CnnJp4ae</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="1" t="inlineStr">
         <is>
-          <t>x6klsVh3</t>
+          <t>bw1zAKS6</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="1" t="inlineStr">
         <is>
-          <t>b3pRrrU7</t>
+          <t>GINCsvmn</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="1" t="inlineStr">
         <is>
-          <t>WfkfPdXH</t>
+          <t>x6klsVh3</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="1" t="inlineStr">
         <is>
-          <t>SMr3Nz2U</t>
+          <t>b3pRrrU7</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="1" t="inlineStr">
         <is>
-          <t>xYBLuIHb</t>
+          <t>WfkfPdXH</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="1" t="inlineStr">
         <is>
-          <t>6os5wmhS</t>
+          <t>SMr3Nz2U</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="1" t="inlineStr">
         <is>
-          <t>Kl7vhn7L</t>
+          <t>xYBLuIHb</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="1" t="inlineStr">
         <is>
-          <t>nw6fJO5K</t>
+          <t>6os5wmhS</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="1" t="inlineStr">
         <is>
-          <t>bHPacsq1</t>
+          <t>Kl7vhn7L</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="1" t="inlineStr">
         <is>
-          <t>MwmHgKaN</t>
+          <t>nw6fJO5K</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="1" t="inlineStr">
         <is>
-          <t>lQl9etVA</t>
+          <t>bHPacsq1</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="1" t="inlineStr">
         <is>
-          <t>KWD8eLDD</t>
+          <t>MwmHgKaN</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="1" t="inlineStr">
         <is>
-          <t>xUXzYQFk</t>
+          <t>lQl9etVA</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="1" t="inlineStr">
         <is>
-          <t>CCV9JR0d</t>
+          <t>KWD8eLDD</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="1" t="inlineStr">
         <is>
-          <t>bsinRI25</t>
+          <t>xUXzYQFk</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="1" t="inlineStr">
         <is>
-          <t>GbaVU03t</t>
+          <t>CCV9JR0d</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" s="1" t="inlineStr">
         <is>
-          <t>tOTmlbNp</t>
+          <t>bsinRI25</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" s="1" t="inlineStr">
         <is>
-          <t>nPQL4PjR</t>
+          <t>GbaVU03t</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" s="1" t="inlineStr">
         <is>
-          <t>pWhdu9NF</t>
+          <t>tOTmlbNp</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" s="1" t="inlineStr">
         <is>
-          <t>6NnRD2Ts</t>
+          <t>nPQL4PjR</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" s="1" t="inlineStr">
         <is>
-          <t>2FcwTvYh</t>
+          <t>pWhdu9NF</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" s="1" t="inlineStr">
         <is>
-          <t>EBSD6oME</t>
+          <t>6NnRD2Ts</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" s="1" t="inlineStr">
         <is>
-          <t>WSQqW4p2</t>
+          <t>2FcwTvYh</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" s="1" t="inlineStr">
         <is>
-          <t>vaX1LmWq</t>
+          <t>EBSD6oME</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" s="1" t="inlineStr">
         <is>
-          <t>n1hhaOVo</t>
+          <t>WSQqW4p2</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" s="1" t="inlineStr">
         <is>
-          <t>vyoZBtbf</t>
+          <t>vaX1LmWq</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" s="1" t="inlineStr">
         <is>
-          <t>634r8bcJ</t>
+          <t>n1hhaOVo</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" s="1" t="inlineStr">
         <is>
-          <t>pbFTwdnB</t>
+          <t>vyoZBtbf</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" s="1" t="inlineStr">
+        <is>
+          <t>634r8bcJ</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" s="1" t="inlineStr">
+        <is>
+          <t>pbFTwdnB</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" s="1" t="inlineStr">
         <is>
           <t>697ha3El</t>
         </is>
